--- a/T41_V012_Files/T41_V012_Assembled_PCBs_V12.8/Files/T41-Single-PE4312-Attenuator-daughterboard_031426/T41_Single-PE4312-Attenuator-daughterboard-ComponentPlacement.xlsx
+++ b/T41_V012_Files/T41_V012_Assembled_PCBs_V12.8/Files/T41-Single-PE4312-Attenuator-daughterboard_031426/T41_Single-PE4312-Attenuator-daughterboard-ComponentPlacement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs\T41_RF_Board_AttenuatorDaughterboard_V1_031426\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_Assembled_PCBs_V12.8\Files\T41-Single-PE4312-Attenuator-daughterboard_031426\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06208B7C-3F87-4350-BE9A-9B6BEFAFBAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E1D526-C3B4-4B26-806C-E6B1F45766CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1AEC1B75-0330-45F2-BE03-9CD656EDC538}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1AEC1B75-0330-45F2-BE03-9CD656EDC538}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -498,15 +498,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2FA298-3F36-4B83-A2A0-D10BDC731DD2}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" customWidth="1"/>
-    <col min="4" max="5" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="12.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="5" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -523,7 +523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -540,7 +540,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -557,7 +557,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -574,7 +574,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -591,7 +591,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -605,10 +605,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
